--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-nuva.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1108</t>
+    <t>1.0.1110</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T00:00:00+00:00</t>
+    <t>2026-06-05T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
